--- a/library/ai-mini-drama/android/cases.xlsx
+++ b/library/ai-mini-drama/android/cases.xlsx
@@ -2042,10 +2042,10 @@
     <t>TC-389</t>
   </si>
   <si>
-    <t>Storyboard generating; a scene with a Location</t>
-  </si>
-  <si>
-    <t>Open that scene's detail while it generates and watch the Location thumbnail</t>
+    <t>Scene detail (Scene edit page) open while that scene's Location image is still generating: the scene regenerated from Edit (TC-070) or updated through Iris (TC-073)</t>
+  </si>
+  <si>
+    <t>Watch the Location thumbnail under the main image until both images finish</t>
   </si>
   <si>
     <t>The Location thumbnail shows a skeleton, then the location image before the main image finishes; the main image keeps its width</t>
@@ -2054,7 +2054,7 @@
     <t>R-299</t>
   </si>
   <si>
-    <t>PM 10/14 board 6; TC-066 notes the Design draws no 「Location」 label</t>
+    <t>PM 10/14 board 6 「10/12 update - Scene 編輯頁的「地點圖片」」: the rule is for the Scene edit page only. The chat storyboard card shows one skeleton loader (Design) and is not this row; if no scene detail can be opened while its Location generates, record Blocked (test-data), not a finding on another screen (Android DRA262610P0345 was filed from that misreading; PDRA 2026-10-29, REQ-055). TC-066 notes the Design draws no 「Location」 label</t>
   </si>
   <si>
     <t>TC-390</t>

--- a/library/ai-mini-drama/android/cases.xlsx
+++ b/library/ai-mini-drama/android/cases.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3988" uniqueCount="2556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4036" uniqueCount="2587">
   <si>
     <t>ID</t>
   </si>
@@ -1466,7 +1466,7 @@
     <t>Ask in chat to change one character's look clearly (e.g. 「Make The Manager a woman in her 40s」); read every message up to the card</t>
   </si>
   <si>
-    <t>No question first; 「Ready to update your characters?」 with the card 「Update characters • 1 character • ◆{price} • Generate」, the price being one character generation; before Generate nothing else is posted: no new Story Outline &amp; Characters card and no message saying characters or storyboard beats were updated</t>
+    <t>No question first; 「Ready to update your characters?」 with the card 「Update characters • 1 character • ◆{price} • Generate」, the price being one character generation (◆6); before Generate nothing else is posted: no new Story Outline &amp; Characters card and no message saying characters or storyboard beats were updated</t>
   </si>
   <si>
     <t>R-038, R-309, R-254 (board-notes l.301-304: Then a charge card "Ready to update your characters?" — **Update characters • {n} character(s) • ◆{credits} • Generate** ... Generate: card disappears, "Working on it..."; ... Done: "Here's your updated cast." + a new Story Outline &amp; Characters card)</t>
@@ -1772,13 +1772,13 @@
     <t>Tap Generate</t>
   </si>
   <si>
-    <t>「Thinking...」 while pricing, then the storyboard generates and the charged credits match the price shown; Mine › Credits › Details books it as Text to Image rows (2 credits per image) and a Text to Speech row that add up to that price</t>
+    <t>「Thinking...」 while pricing, then the storyboard generates and the charged credits match the price shown; Mine › Credits › Details books it as Text to Image rows (6 credits per scene image) and a Text to Speech row that add up to that price</t>
   </si>
   <si>
     <t>R-050</t>
   </si>
   <si>
-    <t>Android ticket DRA262610P0198 (Assigned, AIFound): six scenes quoted and charged 34 credits while the article says 2 credits per image; check the Credit Details rows add up to images × 2 plus TTS</t>
+    <t>Original price from the MX ③ charging sheet 「AI Mini Drama CMS」 › 「Action ID (not on CMS)」 (2026-10-20); original prices are the default and the promotion price is held until the user says it applies (user 2026-10-29, REQ-059). Android ticket DRA262610P0198 (Assigned, AIFound): six scenes quoted and charged 34 credits while the article says 2 credits per image; check the Credit Details rows add up to images × 2 plus TTS</t>
   </si>
   <si>
     <t>TC-377</t>
@@ -2237,7 +2237,7 @@
     <t>Ask in chat 「Update the image for Scene 2 to show rain」</t>
   </si>
   <si>
-    <t>Iris replies with a 「Create storyboard」 card with the price (2 credits per image) and Generate</t>
+    <t>Iris replies with a 「Create storyboard」 card with the price (6 credits per image) and Generate</t>
   </si>
   <si>
     <t>R-061</t>
@@ -2474,7 +2474,7 @@
     <t>Switch Best, Standard and Fast with Preview • 30 sec, then with Full Video</t>
   </si>
   <si>
-    <t>Preview • 30 sec costs ◆180 (Best), ◆120 (Standard), ◆60 (Fast); Full Video costs 6 / 4 / 2 credits per second of its length (◆540 / ◆360 / ◆180 for 90 sec); the price updates at once</t>
+    <t>Preview • 30 sec costs ◆180 (Best), ◆390 (Standard), ◆120 (Fast); Full Video costs 6 / 13 / 4 credits per second of its length (◆540 / ◆1170 / ◆360 for 90 sec); the price updates at once</t>
   </si>
   <si>
     <t>R-069, R-309</t>
@@ -2786,7 +2786,7 @@
     <t>Preview video finished</t>
   </si>
   <si>
-    <t>「Here's your drama.」 with the video card, then 「Looking good! Ready for the full video?」 with 「Create the full episode (90 sec)」 and price</t>
+    <t>「Here's your drama.」 with the video card, then 「Looking good! Ready for the full video?」 with 「Create the full episode (90 sec)��� and price</t>
   </si>
   <si>
     <t>R-075</t>
@@ -3107,7 +3107,7 @@
     <t>Tap Retry; if it fails again tap Edit</t>
   </si>
   <si>
-    <t>「Couldn't create scene」/「Something went wrong. Give it another try.」 with Retry; then 「Retrying didn't work. Try a different description.」 with Edit → editor → Regenerate scene ◆30</t>
+    <t>「Couldn't create scene」/「Something went wrong. Give it another try.」 with Retry; then 「Retrying didn't work. Try a different description.」 with Edit → editor → Regenerate scene priced at the scene's length × the drama model's rate (13 per second Seedance 2.0, 4 Seedance 2.0 Mini, 6 Seedance 2.5; a 15 s scene → ◆195 / ◆60 / ◆90)</t>
   </si>
   <si>
     <t>R-081, R-309</t>
@@ -3698,7 +3698,7 @@
     <t>Look at the 「Create storyboard」 card; create one storyboard, then look at the next card</t>
   </si>
   <si>
-    <t>The price ◆15 is struck through with 「Free • {n} left」, {n} = tries left; the next card shows one fewer</t>
+    <t>The storyboard price (◆6 per scene image plus the Text to Speech part, as TC-060; Design draws ◆15) is struck through with 「Free • {n} left」, {n} = tries left; the next card shows one fewer</t>
   </si>
   <si>
     <t>R-099, R-259, R-309</t>
@@ -3716,7 +3716,7 @@
     <t>Look at the 「Create storyboard」 card</t>
   </si>
   <si>
-    <t>Only the price shows (e.g. ◆15): no strikethrough and no 「Free」</t>
+    <t>Only the price shows (◆6 per scene image plus Text to Speech, as TC-060): no strikethrough and no 「Free」</t>
   </si>
   <si>
     <t>R-260</t>
@@ -5345,13 +5345,31 @@
     <t>Look at the price of each action card in a new drama</t>
   </si>
   <si>
-    <t>Full prices; no credit discount shown</t>
+    <t>Full (original) prices of the charging sheet: ◆6 per character image, ◆6 per storyboard scene image (plus Text to Speech), 13 credits per second for Seedance 2.0 and 4 for Seedance 2.0 Mini (6 for Seedance 2.5, PM 10/16); no credit discount shown</t>
   </si>
   <si>
     <t>R-147</t>
   </si>
   <si>
-    <t>Credit numbers are binding (user rule 2026-10-19); prices from Design until the credit-usage link arrives</t>
+    <t>Original price from the MX ③ charging sheet 「AI Mini Drama CMS」 › 「Action ID (not on CMS)」 (2026-10-20); original prices are the default and the promotion price is held until the user says it applies (user 2026-10-29, REQ-059).</t>
+  </si>
+  <si>
+    <t>TC-544</t>
+  </si>
+  <si>
+    <t>Tier Pro (the signed-in account's own PowerDirector Pro subscription; Android 16.8 has no tier switch); logcat capture running (device-android.ts logcat start)</t>
+  </si>
+  <si>
+    <t>Generate the characters of a new drama (Generate on the characters card), then pull the logs (device-android.ts pull-logs) and read the charge line in logcat</t>
+  </si>
+  <si>
+    <t>The character charge is booked under `genimage_1_img_openai_gptimage2_&lt;none|enable&gt;_1K_aiminidrama_normal` (logcat `action_id`); its `total_credit` is ◆6 × the number of images, the amount Mine › Credits › Details shows for it</t>
+  </si>
+  <si>
+    <t>R-481, R-147</t>
+  </si>
+  <si>
+    <t>Original price from the MX ③ charging sheet 「AI Mini Drama CMS」 › 「Action ID (not on CMS)」 (2026-10-20); original prices are the default and the promotion price is held until the user says it applies (user 2026-10-29, REQ-059). Android 16.8 logcat (A2, 2026-10-27) booked video charges as `genvideo_1_sec_bytedance_seedance2.0std_none_480p_aiminidrama` with no _normal / _discount suffix; record what the build logs. Needs a Pro account (paid-tier), as TC-229.</t>
   </si>
   <si>
     <t>TC-230</t>
@@ -5366,19 +5384,46 @@
     <t>Full prices; no credit discount</t>
   </si>
   <si>
-    <t>TC-231</t>
-  </si>
-  <si>
-    <t>Tier Free; subscribe (sandbox) from the limit dialog or a not-enough card in this session</t>
-  </si>
-  <si>
-    <t>Continue the drama and look at each action card price</t>
-  </si>
-  <si>
-    <t>This session's actions show the discounted price</t>
-  </si>
-  <si>
-    <t>Discount amount is in the MX credit charging table (not in the PDF); record it. Needs a sandbox subscription</t>
+    <t>TC-545</t>
+  </si>
+  <si>
+    <t>Tier Pro (the signed-in account's own PowerDirector Pro subscription; Android 16.8 has no tier switch); characters done; logcat capture running (device-android.ts logcat start)</t>
+  </si>
+  <si>
+    <t>Tap Generate on the 「Create storyboard」 card; then pull the logs (device-android.ts pull-logs) and read the charge line in logcat</t>
+  </si>
+  <si>
+    <t>The card prices the storyboard at 6 credits per scene image (plus Text to Speech, as TC-060) and that amount is charged (Mine › Credits › Details); logcat books it under action_id= `genimage_1_img_openai_gptimage2_&lt;none|enable&gt;_1K_aiminidrama_normal`</t>
+  </si>
+  <si>
+    <t>R-481, R-050</t>
+  </si>
+  <si>
+    <t>Original price from the MX ③ charging sheet 「AI Mini Drama CMS」 › 「Action ID (not on CMS)」 (2026-10-20); original prices are the default and the promotion price is held until the user says it applies (user 2026-10-29, REQ-059). Was the discount row of the TC-231 session (REQ-057).</t>
+  </si>
+  <si>
+    <t>TC-546</t>
+  </si>
+  <si>
+    <t>Tier Pro (the signed-in account's own PowerDirector Pro subscription; Android 16.8 has no tier switch); storyboard done; video settings card shown; logcat capture running (device-android.ts logcat start)</t>
+  </si>
+  <si>
+    <t>Choose Standard (Seedance 2.0) and the Preview length, read the price, tap Generate; then pull the logs (device-android.ts pull-logs) and read the charge line in logcat</t>
+  </si>
+  <si>
+    <t>The card prices the video at 13 credits per second (Preview · 30 sec → ◆390) and that amount is charged (Mine › Credits › Details); logcat books it under action_id= `genvideo_1_sec_bytedance_seedance2.0std_enable_1080p_aiminidrama_normal`</t>
+  </si>
+  <si>
+    <t>R-481, R-069</t>
+  </si>
+  <si>
+    <t>TC-547</t>
+  </si>
+  <si>
+    <t>Choose Fast (Seedance 2.0 Mini) and the Preview length, read the price, tap Generate; then pull the logs (device-android.ts pull-logs) and read the charge line in logcat</t>
+  </si>
+  <si>
+    <t>The card prices the video at 4 credits per second (Preview · 30 sec → ◆120) and that amount is charged (Mine › Credits › Details); logcat books it under action_id= `genvideo_1_sec_bytedance_seedance2.0mini_enable_720p_aiminidrama_normal`</t>
   </si>
   <si>
     <t>TC-232</t>
@@ -5405,6 +5450,54 @@
     <t>Charged at full price</t>
   </si>
   <si>
+    <t>TC-548</t>
+  </si>
+  <si>
+    <t>Tier Pro (the signed-in account's own PowerDirector Pro subscription; Android 16.8 has no tier switch); characters generated; logcat capture running (device-android.ts logcat start)</t>
+  </si>
+  <si>
+    <t>Regenerate one character (ask in chat to change its look, then Generate on the 「Update characters」 card, as TC-045); then pull the logs (device-android.ts pull-logs) and read the charge line in logcat</t>
+  </si>
+  <si>
+    <t>The 「Update characters」 card shows ◆6 per character and that amount is charged (Mine › Credits › Details); logcat books it under action_id= `genimage_1_img_openai_gptimage2_&lt;none|enable&gt;_1K_aiminidrama_normal`</t>
+  </si>
+  <si>
+    <t>R-481, R-254</t>
+  </si>
+  <si>
+    <t>Original price from the MX ③ charging sheet 「AI Mini Drama CMS」 › 「Action ID (not on CMS)」 (2026-10-20); original prices are the default and the promotion price is held until the user says it applies (user 2026-10-29, REQ-059). Was the no-discount regenerate row of the TC-231 session (REQ-057).</t>
+  </si>
+  <si>
+    <t>TC-549</t>
+  </si>
+  <si>
+    <t>Tier Pro (the signed-in account's own PowerDirector Pro subscription; Android 16.8 has no tier switch); storyboard done; logcat capture running (device-android.ts logcat start)</t>
+  </si>
+  <si>
+    <t>Open a scene, tap Edit, change the description, tap Done and 「Regenerate Image」 (as TC-070); then pull the logs (device-android.ts pull-logs) and read the charge line in logcat</t>
+  </si>
+  <si>
+    <t>「Regenerate Image」 shows ◆6 (as TC-070) and that amount is charged (Mine › Credits › Details); logcat books it under action_id= `genimage_1_img_openai_gptimage2_&lt;none|enable&gt;_1K_aiminidrama_normal`</t>
+  </si>
+  <si>
+    <t>R-481, R-059</t>
+  </si>
+  <si>
+    <t>TC-550</t>
+  </si>
+  <si>
+    <t>Tier Pro (the signed-in account's own PowerDirector Pro subscription; Android 16.8 has no tier switch); scene videos done; logcat capture running (device-android.ts logcat start)</t>
+  </si>
+  <si>
+    <t>Regenerate one scene video (Edit its description in the scene editor, then 「Regenerate Video」, as TC-144); then pull the logs (device-android.ts pull-logs) and read the charge line in logcat</t>
+  </si>
+  <si>
+    <t>The regeneration shows and charges the scene's length × the drama model's rate (13 per second Seedance 2.0, 4 Seedance 2.0 Mini, 6 Seedance 2.5; a 15 s scene → ◆195 / ◆60 / ◆90), and Mine › Credits › Details shows that amount; logcat books it under action_id= the model's `genvideo_1_sec_bytedance_seedance2.0&lt;std|mini&gt;_enable_&lt;1080p|720p&gt;_aiminidrama_normal` id</t>
+  </si>
+  <si>
+    <t>R-481, R-081</t>
+  </si>
+  <si>
     <t>TC-234</t>
   </si>
   <si>
@@ -6803,7 +6896,7 @@
     <t>Read the description and the button</t>
   </si>
   <si>
-    <t>Plain editable text in four sections with their headings 「Cinematic Style」, 「Scene」, 「Motion」, 「Camera」, one paragraph each; 「Regenerate scene ◆30」 below</t>
+    <t>Plain editable text in four sections with their headings 「Cinematic Style」, 「Scene」, 「Motion」, 「Camera」, one paragraph each; 「Regenerate scene ◆{price}」 below, {price} = the scene's length × the drama model's rate (13 per second Seedance 2.0, 4 Seedance 2.0 Mini, 6 Seedance 2.5; a 15 s scene → ◆195 / ◆60 / ◆90)</t>
   </si>
   <si>
     <t>R-175</t>
@@ -7649,19 +7742,19 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4</t>
+    <t>6</t>
   </si>
   <si>
     <t>Approved</t>
   </si>
   <si>
-    <t>2026-10-29T03:14:34.064Z</t>
+    <t>2026-10-29T07:32:49.836Z</t>
   </si>
   <si>
     <t>Cases</t>
   </si>
   <si>
-    <t>495</t>
+    <t>501</t>
   </si>
   <si>
     <t>Spec set SHA-256</t>
@@ -8076,7 +8169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H496"/>
+  <dimension ref="A1:H502"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -16791,27 +16884,27 @@
         <v>27</v>
       </c>
       <c r="G335" s="3" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="H335" s="3" t="s">
-        <v>15</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>298</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>27</v>
@@ -16820,111 +16913,111 @@
         <v>1778</v>
       </c>
       <c r="H336" s="3" t="s">
-        <v>1788</v>
+        <v>15</v>
       </c>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>298</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G337" s="3" t="s">
-        <v>1778</v>
+        <v>1794</v>
       </c>
       <c r="H337" s="3" t="s">
-        <v>15</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>298</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="D338" s="3" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E338" s="3" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F338" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G338" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="H338" s="3" t="s">
         <v>1795</v>
-      </c>
-      <c r="E338" s="3" t="s">
-        <v>1796</v>
-      </c>
-      <c r="F338" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G338" s="3" t="s">
-        <v>1778</v>
-      </c>
-      <c r="H338" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C339" s="3" t="s">
         <v>1797</v>
       </c>
-      <c r="B339" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C339" s="3" t="s">
-        <v>1798</v>
-      </c>
       <c r="D339" s="3" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="E339" s="3" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F339" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G339" s="3" t="s">
         <v>1800</v>
       </c>
-      <c r="F339" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G339" s="3" t="s">
-        <v>1801</v>
-      </c>
       <c r="H339" s="3" t="s">
-        <v>1802</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>59</v>
+        <v>298</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G340" s="3" t="s">
-        <v>1801</v>
+        <v>1778</v>
       </c>
       <c r="H340" s="3" t="s">
-        <v>1807</v>
+        <v>15</v>
       </c>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
@@ -16932,7 +17025,7 @@
         <v>1808</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>59</v>
+        <v>298</v>
       </c>
       <c r="C341" s="3" t="s">
         <v>1809</v>
@@ -16944,76 +17037,76 @@
         <v>1811</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G341" s="3" t="s">
-        <v>1801</v>
+        <v>1778</v>
       </c>
       <c r="H341" s="3" t="s">
-        <v>1812</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C342" s="3" t="s">
         <v>1813</v>
       </c>
-      <c r="B342" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C342" s="3" t="s">
+      <c r="D342" s="3" t="s">
         <v>1814</v>
       </c>
-      <c r="D342" s="3" t="s">
+      <c r="E342" s="3" t="s">
         <v>1815</v>
       </c>
-      <c r="E342" s="3" t="s">
+      <c r="F342" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G342" s="3" t="s">
         <v>1816</v>
       </c>
-      <c r="F342" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G342" s="3" t="s">
+      <c r="H342" s="3" t="s">
         <v>1817</v>
-      </c>
-      <c r="H342" s="3" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C343" s="3" t="s">
         <v>1819</v>
       </c>
-      <c r="B343" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C343" s="3" t="s">
+      <c r="D343" s="3" t="s">
         <v>1820</v>
       </c>
-      <c r="D343" s="3" t="s">
+      <c r="E343" s="3" t="s">
         <v>1821</v>
       </c>
-      <c r="E343" s="3" t="s">
+      <c r="F343" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G343" s="3" t="s">
         <v>1822</v>
       </c>
-      <c r="F343" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G343" s="3" t="s">
-        <v>235</v>
-      </c>
       <c r="H343" s="3" t="s">
-        <v>1823</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C344" s="3" t="s">
         <v>1824</v>
-      </c>
-      <c r="B344" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C344" s="3" t="s">
-        <v>1820</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>1825</v>
@@ -17025,10 +17118,10 @@
         <v>27</v>
       </c>
       <c r="G344" s="3" t="s">
-        <v>235</v>
+        <v>1827</v>
       </c>
       <c r="H344" s="3" t="s">
-        <v>1827</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
@@ -17039,1709 +17132,1709 @@
         <v>59</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>1820</v>
+        <v>1829</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G345" s="3" t="s">
-        <v>235</v>
+        <v>1832</v>
       </c>
       <c r="H345" s="3" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G346" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H346" s="3" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1810</v>
+        <v>1841</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1811</v>
+        <v>1842</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G347" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H347" s="3" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G348" s="3" t="s">
-        <v>1801</v>
+        <v>1848</v>
       </c>
       <c r="H348" s="3" t="s">
-        <v>1844</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
-        <v>1845</v>
+        <v>1850</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>1846</v>
+        <v>1851</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1847</v>
+        <v>1852</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1848</v>
+        <v>1853</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G349" s="3" t="s">
-        <v>1849</v>
+        <v>235</v>
       </c>
       <c r="H349" s="3" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1810</v>
+        <v>1856</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1811</v>
+        <v>1857</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G350" s="3" t="s">
-        <v>1801</v>
+        <v>235</v>
       </c>
       <c r="H350" s="3" t="s">
-        <v>1853</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
-        <v>1854</v>
+        <v>1859</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>1855</v>
+        <v>1851</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
       <c r="F351" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G351" s="3" t="s">
-        <v>1817</v>
+        <v>235</v>
       </c>
       <c r="H351" s="3" t="s">
-        <v>1858</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G352" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H352" s="3" t="s">
-        <v>1863</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
-        <v>1864</v>
+        <v>1868</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>1865</v>
+        <v>1869</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1866</v>
+        <v>1841</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>1867</v>
+        <v>1842</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G353" s="3" t="s">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="H353" s="3" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1810</v>
+        <v>1873</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1811</v>
+        <v>1874</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G354" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H354" s="3" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G355" s="3" t="s">
-        <v>1801</v>
+        <v>1880</v>
       </c>
       <c r="H355" s="3" t="s">
-        <v>1876</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
-        <v>1877</v>
+        <v>1882</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>1878</v>
+        <v>1883</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1879</v>
+        <v>1841</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1880</v>
+        <v>1842</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G356" s="3" t="s">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="H356" s="3" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1810</v>
+        <v>1887</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1811</v>
+        <v>1888</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G357" s="3" t="s">
-        <v>1801</v>
+        <v>1848</v>
       </c>
       <c r="H357" s="3" t="s">
-        <v>1884</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
-        <v>1885</v>
+        <v>1890</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1886</v>
+        <v>1891</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>1887</v>
+        <v>1892</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>1888</v>
+        <v>1893</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G358" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H358" s="3" t="s">
-        <v>1889</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
-        <v>1890</v>
+        <v>1895</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1891</v>
+        <v>1896</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>1810</v>
+        <v>1897</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>1811</v>
+        <v>1898</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G359" s="3" t="s">
-        <v>1801</v>
+        <v>1899</v>
       </c>
       <c r="H359" s="3" t="s">
-        <v>1892</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
-        <v>1893</v>
+        <v>1901</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>1895</v>
+        <v>1841</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1896</v>
+        <v>1842</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G360" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H360" s="3" t="s">
-        <v>1897</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
-        <v>1898</v>
+        <v>1903</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>1899</v>
+        <v>1904</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1810</v>
+        <v>1905</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1811</v>
+        <v>1906</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G361" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H361" s="3" t="s">
-        <v>1900</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
-        <v>1901</v>
+        <v>1908</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>1902</v>
+        <v>1909</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1903</v>
+        <v>1910</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1904</v>
+        <v>1911</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G362" s="3" t="s">
-        <v>1801</v>
+        <v>1899</v>
       </c>
       <c r="H362" s="3" t="s">
-        <v>1905</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
-        <v>1906</v>
+        <v>1913</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>1907</v>
+        <v>1914</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1810</v>
+        <v>1841</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1811</v>
+        <v>1842</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G363" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H363" s="3" t="s">
-        <v>1908</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
-        <v>1909</v>
+        <v>1916</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>1910</v>
+        <v>1917</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1911</v>
+        <v>1918</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1912</v>
+        <v>1919</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G364" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H364" s="3" t="s">
-        <v>1913</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
-        <v>1914</v>
+        <v>1921</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>1915</v>
+        <v>1922</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1810</v>
+        <v>1841</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1811</v>
+        <v>1842</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G365" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H365" s="3" t="s">
-        <v>1916</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
-        <v>1917</v>
+        <v>1924</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>1918</v>
+        <v>1925</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1919</v>
+        <v>1926</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1920</v>
+        <v>1927</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G366" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H366" s="3" t="s">
-        <v>1921</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
-        <v>1922</v>
+        <v>1929</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>1923</v>
+        <v>1930</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1810</v>
+        <v>1841</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1811</v>
+        <v>1842</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G367" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H367" s="3" t="s">
-        <v>1924</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
-        <v>1925</v>
+        <v>1932</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>1926</v>
+        <v>1933</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1927</v>
+        <v>1934</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1928</v>
+        <v>1935</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G368" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H368" s="3" t="s">
-        <v>1929</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
-        <v>1930</v>
+        <v>1937</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>1931</v>
+        <v>1938</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1810</v>
+        <v>1841</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1811</v>
+        <v>1842</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G369" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H369" s="3" t="s">
-        <v>1932</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
-        <v>1933</v>
+        <v>1940</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>1934</v>
+        <v>1941</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1935</v>
+        <v>1942</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1936</v>
+        <v>1943</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G370" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H370" s="3" t="s">
-        <v>1937</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
-        <v>1938</v>
+        <v>1945</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>1939</v>
+        <v>1946</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1810</v>
+        <v>1841</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1811</v>
+        <v>1842</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G371" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H371" s="3" t="s">
-        <v>1940</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
-        <v>1941</v>
+        <v>1948</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>1942</v>
+        <v>1949</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1943</v>
+        <v>1950</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1944</v>
+        <v>1951</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G372" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H372" s="3" t="s">
-        <v>1945</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
-        <v>1946</v>
+        <v>1953</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>1947</v>
+        <v>1954</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1948</v>
+        <v>1841</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1949</v>
+        <v>1842</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G373" s="3" t="s">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="H373" s="3" t="s">
-        <v>1950</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
-        <v>1951</v>
+        <v>1956</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>1947</v>
+        <v>1957</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1810</v>
+        <v>1958</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1811</v>
+        <v>1959</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G374" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H374" s="3" t="s">
-        <v>1952</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
-        <v>1953</v>
+        <v>1961</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>1955</v>
+        <v>1841</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>1956</v>
+        <v>1842</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G375" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H375" s="3" t="s">
-        <v>1957</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>1959</v>
+        <v>1965</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>1810</v>
+        <v>1966</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1811</v>
+        <v>1967</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G376" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H376" s="3" t="s">
-        <v>1960</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
-        <v>1961</v>
+        <v>1969</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>1962</v>
+        <v>1970</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>1963</v>
+        <v>1841</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>1964</v>
+        <v>1842</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G377" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H377" s="3" t="s">
-        <v>1965</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>1967</v>
+        <v>1973</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1810</v>
+        <v>1974</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1811</v>
+        <v>1975</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G378" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H378" s="3" t="s">
-        <v>1968</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
-        <v>1969</v>
+        <v>1977</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1971</v>
+        <v>1979</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G379" s="3" t="s">
-        <v>1801</v>
+        <v>1899</v>
       </c>
       <c r="H379" s="3" t="s">
-        <v>1973</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
-        <v>1974</v>
+        <v>1982</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1976</v>
+        <v>1841</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1977</v>
+        <v>1842</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G380" s="3" t="s">
-        <v>88</v>
+        <v>1832</v>
       </c>
       <c r="H380" s="3" t="s">
-        <v>1978</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1810</v>
+        <v>1986</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1811</v>
+        <v>1987</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G381" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H381" s="3" t="s">
-        <v>1981</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
-        <v>1982</v>
+        <v>1989</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>1983</v>
+        <v>1990</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1984</v>
+        <v>1841</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1985</v>
+        <v>1842</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G382" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H382" s="3" t="s">
-        <v>1986</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
-        <v>1987</v>
+        <v>1992</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>1988</v>
+        <v>1993</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1810</v>
+        <v>1994</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1811</v>
+        <v>1995</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G383" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H383" s="3" t="s">
-        <v>1989</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
-        <v>1990</v>
+        <v>1997</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>1991</v>
+        <v>1998</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1992</v>
+        <v>1841</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1993</v>
+        <v>1842</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G384" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H384" s="3" t="s">
-        <v>1994</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
-        <v>1995</v>
+        <v>2000</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>1996</v>
+        <v>2001</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G385" s="3" t="s">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="H385" s="3" t="s">
-        <v>1999</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>1996</v>
+        <v>2006</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G386" s="3" t="s">
-        <v>1868</v>
+        <v>88</v>
       </c>
       <c r="H386" s="3" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1810</v>
+        <v>1841</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>1811</v>
+        <v>1842</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G387" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H387" s="3" t="s">
-        <v>2006</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G388" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H388" s="3" t="s">
-        <v>2011</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>2014</v>
+        <v>1841</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>2015</v>
+        <v>1842</v>
       </c>
       <c r="F389" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G389" s="3" t="s">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="H389" s="3" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G390" s="3" t="s">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="H390" s="3" t="s">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1810</v>
+        <v>2028</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>1811</v>
+        <v>2029</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G391" s="3" t="s">
-        <v>1801</v>
+        <v>1899</v>
       </c>
       <c r="H391" s="3" t="s">
-        <v>2022</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>2025</v>
+        <v>2032</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>2026</v>
+        <v>2033</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G392" s="3" t="s">
-        <v>1801</v>
+        <v>1899</v>
       </c>
       <c r="H392" s="3" t="s">
-        <v>2027</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
-        <v>2028</v>
+        <v>2035</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>2029</v>
+        <v>2036</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1948</v>
+        <v>1841</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>2030</v>
+        <v>1842</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G393" s="3" t="s">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="H393" s="3" t="s">
-        <v>2031</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>2029</v>
+        <v>2039</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1810</v>
+        <v>2040</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>1811</v>
+        <v>2041</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G394" s="3" t="s">
-        <v>1801</v>
+        <v>1832</v>
       </c>
       <c r="H394" s="3" t="s">
-        <v>2033</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
-        <v>2034</v>
+        <v>2043</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>2035</v>
+        <v>59</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>2036</v>
+        <v>2044</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>2037</v>
+        <v>2045</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>2038</v>
+        <v>2046</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G395" s="3" t="s">
-        <v>2039</v>
+        <v>1899</v>
       </c>
       <c r="H395" s="3" t="s">
-        <v>15</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
-        <v>2040</v>
+        <v>2048</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>2035</v>
+        <v>59</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>2038</v>
+        <v>2049</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G396" s="3" t="s">
-        <v>2039</v>
+        <v>1899</v>
       </c>
       <c r="H396" s="3" t="s">
-        <v>2042</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
-        <v>2043</v>
+        <v>2051</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>2035</v>
+        <v>59</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>2044</v>
+        <v>2052</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>2037</v>
+        <v>1841</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>2038</v>
+        <v>1842</v>
       </c>
       <c r="F397" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G397" s="3" t="s">
-        <v>2039</v>
+        <v>1832</v>
       </c>
       <c r="H397" s="3" t="s">
-        <v>2045</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
-        <v>2046</v>
+        <v>2054</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>2035</v>
+        <v>59</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>2047</v>
+        <v>2055</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>2048</v>
+        <v>2056</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>2049</v>
+        <v>2057</v>
       </c>
       <c r="F398" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G398" s="3" t="s">
-        <v>2050</v>
+        <v>1832</v>
       </c>
       <c r="H398" s="3" t="s">
-        <v>2051</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
-        <v>2052</v>
+        <v>2059</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>2035</v>
+        <v>59</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>2053</v>
+        <v>2060</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>2037</v>
+        <v>1979</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>2054</v>
+        <v>2061</v>
       </c>
       <c r="F399" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G399" s="3" t="s">
-        <v>2055</v>
+        <v>1899</v>
       </c>
       <c r="H399" s="3" t="s">
-        <v>2056</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
-        <v>2057</v>
+        <v>2063</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>2035</v>
+        <v>59</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>652</v>
+        <v>2060</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>2058</v>
+        <v>1841</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>2059</v>
+        <v>1842</v>
       </c>
       <c r="F400" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G400" s="3" t="s">
-        <v>2060</v>
+        <v>1832</v>
       </c>
       <c r="H400" s="3" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>2035</v>
+        <v>2066</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>2063</v>
+        <v>2067</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>2064</v>
+        <v>2068</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>2065</v>
+        <v>2069</v>
       </c>
       <c r="F401" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G401" s="3" t="s">
-        <v>235</v>
+        <v>2070</v>
       </c>
       <c r="H401" s="3" t="s">
-        <v>2066</v>
+        <v>15</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>2035</v>
+        <v>2066</v>
       </c>
       <c r="C402" s="3" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D402" s="3" t="s">
         <v>2068</v>
       </c>
-      <c r="D402" s="3" t="s">
+      <c r="E402" s="3" t="s">
         <v>2069</v>
       </c>
-      <c r="E402" s="3" t="s">
+      <c r="F402" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G402" s="3" t="s">
         <v>2070</v>
       </c>
-      <c r="F402" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G402" s="3" t="s">
-        <v>235</v>
-      </c>
       <c r="H402" s="3" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" s="3" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>2035</v>
+        <v>2066</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>652</v>
+        <v>2075</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="F403" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G403" s="3" t="s">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="H403" s="3" t="s">
-        <v>15</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>2035</v>
+        <v>2066</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>652</v>
+        <v>2078</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G404" s="3" t="s">
-        <v>2060</v>
+        <v>2081</v>
       </c>
       <c r="H404" s="3" t="s">
-        <v>15</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
-        <v>2078</v>
+        <v>2083</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>2035</v>
+        <v>2066</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>652</v>
+        <v>2084</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>2079</v>
+        <v>2068</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>2080</v>
+        <v>2085</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G405" s="3" t="s">
-        <v>2060</v>
+        <v>2086</v>
       </c>
       <c r="H405" s="3" t="s">
-        <v>15</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
-        <v>2081</v>
+        <v>2088</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>2035</v>
+        <v>2066</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>652</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>2082</v>
+        <v>2089</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>2083</v>
+        <v>2090</v>
       </c>
       <c r="F406" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G406" s="3" t="s">
-        <v>2060</v>
+        <v>2091</v>
       </c>
       <c r="H406" s="3" t="s">
-        <v>2084</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
-        <v>2085</v>
+        <v>2093</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>2035</v>
+        <v>2066</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>2086</v>
+        <v>2094</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>2087</v>
+        <v>2095</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>2088</v>
+        <v>2096</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G407" s="3" t="s">
-        <v>2089</v>
+        <v>235</v>
       </c>
       <c r="H407" s="3" t="s">
-        <v>2090</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
-        <v>2091</v>
+        <v>2098</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>500</v>
+        <v>2066</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>2092</v>
+        <v>2099</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>2093</v>
+        <v>2100</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>2094</v>
+        <v>2101</v>
       </c>
       <c r="F408" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G408" s="3" t="s">
-        <v>2095</v>
+        <v>235</v>
       </c>
       <c r="H408" s="3" t="s">
-        <v>15</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" s="3" t="s">
-        <v>2096</v>
+        <v>2103</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>500</v>
+        <v>2066</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>2097</v>
+        <v>652</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>2098</v>
+        <v>2104</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>2099</v>
+        <v>2105</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G409" s="3" t="s">
-        <v>2100</v>
+        <v>2091</v>
       </c>
       <c r="H409" s="3" t="s">
-        <v>2101</v>
+        <v>15</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>500</v>
+        <v>2066</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>2103</v>
+        <v>652</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>2098</v>
+        <v>2107</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>2099</v>
+        <v>2108</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G410" s="3" t="s">
-        <v>2100</v>
+        <v>2091</v>
       </c>
       <c r="H410" s="3" t="s">
         <v>15</v>
@@ -18749,25 +18842,25 @@
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
-        <v>2104</v>
+        <v>2109</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>97</v>
+        <v>2066</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>2105</v>
+        <v>652</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>2106</v>
+        <v>2110</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>2107</v>
+        <v>2111</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G411" s="3" t="s">
-        <v>2108</v>
+        <v>2091</v>
       </c>
       <c r="H411" s="3" t="s">
         <v>15</v>
@@ -18775,77 +18868,77 @@
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>500</v>
+        <v>2066</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>2110</v>
+        <v>652</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G412" s="3" t="s">
-        <v>2113</v>
+        <v>2091</v>
       </c>
       <c r="H412" s="3" t="s">
-        <v>15</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>362</v>
+        <v>2066</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="F413" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G413" s="3" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="H413" s="3" t="s">
-        <v>15</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>362</v>
+        <v>500</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G414" s="3" t="s">
-        <v>2118</v>
+        <v>2126</v>
       </c>
       <c r="H414" s="3" t="s">
         <v>15</v>
@@ -18853,80 +18946,80 @@
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="3" t="s">
-        <v>2123</v>
+        <v>2127</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>362</v>
+        <v>500</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>2124</v>
+        <v>2128</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>2125</v>
+        <v>2129</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>2126</v>
+        <v>2130</v>
       </c>
       <c r="F415" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G415" s="3" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
       <c r="H415" s="3" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D416" s="3" t="s">
         <v>2129</v>
       </c>
-      <c r="B416" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C416" s="3" t="s">
+      <c r="E416" s="3" t="s">
         <v>2130</v>
       </c>
-      <c r="D416" s="3" t="s">
+      <c r="F416" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G416" s="3" t="s">
         <v>2131</v>
       </c>
-      <c r="E416" s="3" t="s">
-        <v>2132</v>
-      </c>
-      <c r="F416" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G416" s="3" t="s">
-        <v>2127</v>
-      </c>
       <c r="H416" s="3" t="s">
-        <v>2133</v>
+        <v>15</v>
       </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>583</v>
+        <v>97</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G417" s="3" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="H417" s="3" t="s">
-        <v>2139</v>
+        <v>15</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
@@ -18934,7 +19027,7 @@
         <v>2140</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>583</v>
+        <v>500</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>2141</v>
@@ -18946,7 +19039,7 @@
         <v>2143</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G418" s="3" t="s">
         <v>2144</v>
@@ -18960,51 +19053,51 @@
         <v>2145</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>583</v>
+        <v>362</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>2146</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>248</v>
+        <v>2147</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G419" s="3" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>618</v>
+        <v>15</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D420" s="3" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E420" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="F420" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G420" s="3" t="s">
         <v>2149</v>
       </c>
-      <c r="B420" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="C420" s="3" t="s">
-        <v>2150</v>
-      </c>
-      <c r="D420" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E420" s="3" t="s">
-        <v>2151</v>
-      </c>
-      <c r="F420" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G420" s="3" t="s">
-        <v>2152</v>
-      </c>
       <c r="H420" s="3" t="s">
-        <v>2153</v>
+        <v>15</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
@@ -19012,7 +19105,7 @@
         <v>2154</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>583</v>
+        <v>362</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>2155</v>
@@ -19038,7 +19131,7 @@
         <v>2160</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>1005</v>
+        <v>362</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>2161</v>
@@ -19050,13 +19143,13 @@
         <v>2163</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G422" s="3" t="s">
+        <v>2158</v>
+      </c>
+      <c r="H422" s="3" t="s">
         <v>2164</v>
-      </c>
-      <c r="H422" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
@@ -19064,7 +19157,7 @@
         <v>2165</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>805</v>
+        <v>583</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>2166</v>
@@ -19076,39 +19169,39 @@
         <v>2168</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>2169</v>
       </c>
       <c r="H423" s="3" t="s">
-        <v>15</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>1081</v>
+        <v>583</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G424" s="3" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="H424" s="3" t="s">
-        <v>2175</v>
+        <v>15</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
@@ -19116,100 +19209,100 @@
         <v>2176</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>771</v>
+        <v>583</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>2177</v>
       </c>
       <c r="D425" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E425" s="3" t="s">
         <v>2178</v>
       </c>
-      <c r="E425" s="3" t="s">
+      <c r="F425" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G425" s="3" t="s">
         <v>2179</v>
       </c>
-      <c r="F425" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G425" s="3" t="s">
-        <v>2180</v>
-      </c>
       <c r="H425" s="3" t="s">
-        <v>2181</v>
+        <v>618</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>583</v>
       </c>
       <c r="C426" s="3" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D426" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E426" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F426" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G426" s="3" t="s">
         <v>2183</v>
       </c>
-      <c r="D426" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="E426" s="3" t="s">
+      <c r="H426" s="3" t="s">
         <v>2184</v>
-      </c>
-      <c r="F426" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G426" s="3" t="s">
-        <v>2185</v>
-      </c>
-      <c r="H426" s="3" t="s">
-        <v>2186</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="3" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D427" s="3" t="s">
         <v>2187</v>
       </c>
-      <c r="B427" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C427" s="3" t="s">
+      <c r="E427" s="3" t="s">
         <v>2188</v>
       </c>
-      <c r="D427" s="3" t="s">
+      <c r="F427" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G427" s="3" t="s">
         <v>2189</v>
       </c>
-      <c r="E427" s="3" t="s">
+      <c r="H427" s="3" t="s">
         <v>2190</v>
-      </c>
-      <c r="F427" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G427" s="3" t="s">
-        <v>2191</v>
-      </c>
-      <c r="H427" s="3" t="s">
-        <v>2192</v>
       </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B428" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D428" s="3" t="s">
         <v>2193</v>
       </c>
-      <c r="B428" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="C428" s="3" t="s">
+      <c r="E428" s="3" t="s">
         <v>2194</v>
       </c>
-      <c r="D428" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E428" s="3" t="s">
+      <c r="F428" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G428" s="3" t="s">
         <v>2195</v>
-      </c>
-      <c r="F428" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G428" s="3" t="s">
-        <v>2196</v>
       </c>
       <c r="H428" s="3" t="s">
         <v>15</v>
@@ -19217,54 +19310,54 @@
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" s="3" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>805</v>
       </c>
       <c r="C429" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D429" s="3" t="s">
         <v>2198</v>
       </c>
-      <c r="D429" s="3" t="s">
+      <c r="E429" s="3" t="s">
         <v>2199</v>
       </c>
-      <c r="E429" s="3" t="s">
+      <c r="F429" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G429" s="3" t="s">
         <v>2200</v>
       </c>
-      <c r="F429" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G429" s="3" t="s">
-        <v>2201</v>
-      </c>
       <c r="H429" s="3" t="s">
-        <v>2202</v>
+        <v>15</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" s="3" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B430" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D430" s="3" t="s">
         <v>2203</v>
       </c>
-      <c r="B430" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="C430" s="3" t="s">
-        <v>2198</v>
-      </c>
-      <c r="D430" s="3" t="s">
+      <c r="E430" s="3" t="s">
         <v>2204</v>
-      </c>
-      <c r="E430" s="3" t="s">
-        <v>2205</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G430" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="H430" s="3" t="s">
         <v>2206</v>
-      </c>
-      <c r="H430" s="3" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
@@ -19272,7 +19365,7 @@
         <v>2207</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>805</v>
+        <v>771</v>
       </c>
       <c r="C431" s="3" t="s">
         <v>2208</v>
@@ -19284,7 +19377,7 @@
         <v>2210</v>
       </c>
       <c r="F431" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G431" s="3" t="s">
         <v>2211</v>
@@ -19298,51 +19391,51 @@
         <v>2213</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>805</v>
+        <v>583</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>2214</v>
       </c>
       <c r="D432" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E432" s="3" t="s">
         <v>2215</v>
       </c>
-      <c r="E432" s="3" t="s">
+      <c r="F432" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G432" s="3" t="s">
         <v>2216</v>
       </c>
-      <c r="F432" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G432" s="3" t="s">
+      <c r="H432" s="3" t="s">
         <v>2217</v>
-      </c>
-      <c r="H432" s="3" t="s">
-        <v>2218</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" s="3" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C433" s="3" t="s">
         <v>2219</v>
       </c>
-      <c r="B433" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="C433" s="3" t="s">
+      <c r="D433" s="3" t="s">
         <v>2220</v>
       </c>
-      <c r="D433" s="3" t="s">
+      <c r="E433" s="3" t="s">
         <v>2221</v>
       </c>
-      <c r="E433" s="3" t="s">
+      <c r="F433" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G433" s="3" t="s">
         <v>2222</v>
       </c>
-      <c r="F433" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G433" s="3" t="s">
+      <c r="H433" s="3" t="s">
         <v>2223</v>
-      </c>
-      <c r="H433" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.25">
@@ -19350,103 +19443,103 @@
         <v>2224</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>805</v>
+        <v>583</v>
       </c>
       <c r="C434" s="3" t="s">
         <v>2225</v>
       </c>
       <c r="D434" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E434" s="3" t="s">
         <v>2226</v>
       </c>
-      <c r="E434" s="3" t="s">
+      <c r="F434" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G434" s="3" t="s">
         <v>2227</v>
       </c>
-      <c r="F434" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G434" s="3" t="s">
-        <v>2228</v>
-      </c>
       <c r="H434" s="3" t="s">
-        <v>2229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D435" s="3" t="s">
         <v>2230</v>
       </c>
-      <c r="B435" s="3" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C435" s="3" t="s">
+      <c r="E435" s="3" t="s">
         <v>2231</v>
       </c>
-      <c r="D435" s="3" t="s">
+      <c r="F435" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G435" s="3" t="s">
         <v>2232</v>
       </c>
-      <c r="E435" s="3" t="s">
+      <c r="H435" s="3" t="s">
         <v>2233</v>
-      </c>
-      <c r="F435" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G435" s="3" t="s">
-        <v>2234</v>
-      </c>
-      <c r="H435" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D436" s="3" t="s">
         <v>2235</v>
       </c>
-      <c r="B436" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C436" s="3" t="s">
+      <c r="E436" s="3" t="s">
         <v>2236</v>
-      </c>
-      <c r="D436" s="3" t="s">
-        <v>2237</v>
-      </c>
-      <c r="E436" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="F436" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G436" s="3" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="H436" s="3" t="s">
-        <v>383</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C437" s="3" t="s">
         <v>2239</v>
       </c>
-      <c r="B437" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C437" s="3" t="s">
+      <c r="D437" s="3" t="s">
         <v>2240</v>
       </c>
-      <c r="D437" s="3" t="s">
+      <c r="E437" s="3" t="s">
         <v>2241</v>
       </c>
-      <c r="E437" s="3" t="s">
+      <c r="F437" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G437" s="3" t="s">
         <v>2242</v>
       </c>
-      <c r="F437" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G437" s="3" t="s">
+      <c r="H437" s="3" t="s">
         <v>2243</v>
-      </c>
-      <c r="H437" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.25">
@@ -19454,7 +19547,7 @@
         <v>2244</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>1129</v>
+        <v>805</v>
       </c>
       <c r="C438" s="3" t="s">
         <v>2245</v>
@@ -19463,39 +19556,39 @@
         <v>2246</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>1147</v>
+        <v>2247</v>
       </c>
       <c r="F438" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G438" s="3" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="H438" s="3" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" s="3" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>583</v>
+        <v>805</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="F439" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G439" s="3" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="H439" s="3" t="s">
         <v>15</v>
@@ -19503,51 +19596,51 @@
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" s="3" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>583</v>
+        <v>805</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>146</v>
+        <v>2257</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G440" s="3" t="s">
-        <v>2253</v>
+        <v>2259</v>
       </c>
       <c r="H440" s="3" t="s">
-        <v>15</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="3" t="s">
-        <v>2257</v>
+        <v>2261</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>1005</v>
+        <v>1160</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>2258</v>
+        <v>2262</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>2251</v>
+        <v>2263</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>2252</v>
+        <v>2264</v>
       </c>
       <c r="F441" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G441" s="3" t="s">
-        <v>2253</v>
+        <v>2265</v>
       </c>
       <c r="H441" s="3" t="s">
         <v>15</v>
@@ -19555,155 +19648,155 @@
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="3" t="s">
-        <v>2259</v>
+        <v>2266</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>1005</v>
+        <v>362</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>2260</v>
+        <v>2267</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>146</v>
+        <v>2268</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>2256</v>
+        <v>382</v>
       </c>
       <c r="F442" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G442" s="3" t="s">
-        <v>2253</v>
+        <v>2269</v>
       </c>
       <c r="H442" s="3" t="s">
-        <v>15</v>
+        <v>383</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
-        <v>2261</v>
+        <v>2270</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>1005</v>
+        <v>362</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>2258</v>
+        <v>2271</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>2262</v>
+        <v>2272</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>2263</v>
+        <v>2273</v>
       </c>
       <c r="F443" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G443" s="3" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
       <c r="H443" s="3" t="s">
-        <v>2265</v>
+        <v>15</v>
       </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
-        <v>2266</v>
+        <v>2275</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>500</v>
+        <v>1129</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>2267</v>
+        <v>2276</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>2268</v>
+        <v>2277</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>2269</v>
+        <v>1147</v>
       </c>
       <c r="F444" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G444" s="3" t="s">
-        <v>2270</v>
+        <v>2278</v>
       </c>
       <c r="H444" s="3" t="s">
-        <v>15</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" s="3" t="s">
-        <v>2271</v>
+        <v>2280</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>1160</v>
+        <v>583</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>2272</v>
+        <v>2281</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>2273</v>
+        <v>2282</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>2274</v>
+        <v>2283</v>
       </c>
       <c r="F445" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G445" s="3" t="s">
-        <v>2275</v>
+        <v>2284</v>
       </c>
       <c r="H445" s="3" t="s">
-        <v>2276</v>
+        <v>15</v>
       </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
-        <v>2277</v>
+        <v>2285</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>1160</v>
+        <v>583</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>136</v>
+        <v>2286</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>2278</v>
+        <v>146</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>2279</v>
+        <v>2287</v>
       </c>
       <c r="F446" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G446" s="3" t="s">
-        <v>2280</v>
+        <v>2284</v>
       </c>
       <c r="H446" s="3" t="s">
-        <v>2281</v>
+        <v>15</v>
       </c>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D447" s="3" t="s">
         <v>2282</v>
       </c>
-      <c r="B447" s="3" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C447" s="3" t="s">
+      <c r="E447" s="3" t="s">
         <v>2283</v>
-      </c>
-      <c r="D447" s="3" t="s">
-        <v>2273</v>
-      </c>
-      <c r="E447" s="3" t="s">
-        <v>2284</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G447" s="3" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="H447" s="3" t="s">
         <v>15</v>
@@ -19711,39 +19804,39 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" s="3" t="s">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>1160</v>
+        <v>1005</v>
       </c>
       <c r="C448" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D448" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E448" s="3" t="s">
         <v>2287</v>
-      </c>
-      <c r="D448" s="3" t="s">
-        <v>900</v>
-      </c>
-      <c r="E448" s="3" t="s">
-        <v>2288</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G448" s="3" t="s">
-        <v>2289</v>
+        <v>2284</v>
       </c>
       <c r="H448" s="3" t="s">
-        <v>2290</v>
+        <v>15</v>
       </c>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>805</v>
+        <v>1005</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="D449" s="3" t="s">
         <v>2293</v>
@@ -19752,7 +19845,7 @@
         <v>2294</v>
       </c>
       <c r="F449" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G449" s="3" t="s">
         <v>2295</v>
@@ -19766,25 +19859,25 @@
         <v>2297</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>805</v>
+        <v>500</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>2292</v>
+        <v>2298</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="F450" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G450" s="3" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="H450" s="3" t="s">
-        <v>2301</v>
+        <v>15</v>
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
@@ -19792,7 +19885,7 @@
         <v>2302</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>805</v>
+        <v>1160</v>
       </c>
       <c r="C451" s="3" t="s">
         <v>2303</v>
@@ -19804,7 +19897,7 @@
         <v>2305</v>
       </c>
       <c r="F451" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G451" s="3" t="s">
         <v>2306</v>
@@ -19818,48 +19911,48 @@
         <v>2308</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>1598</v>
+        <v>1160</v>
       </c>
       <c r="C452" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D452" s="3" t="s">
         <v>2309</v>
       </c>
-      <c r="D452" s="3" t="s">
+      <c r="E452" s="3" t="s">
         <v>2310</v>
-      </c>
-      <c r="E452" s="3" t="s">
-        <v>2311</v>
       </c>
       <c r="F452" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G452" s="3" t="s">
+        <v>2311</v>
+      </c>
+      <c r="H452" s="3" t="s">
         <v>2312</v>
-      </c>
-      <c r="H452" s="3" t="s">
-        <v>2313</v>
       </c>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B453" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C453" s="3" t="s">
         <v>2314</v>
       </c>
-      <c r="B453" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C453" s="3" t="s">
+      <c r="D453" s="3" t="s">
+        <v>2304</v>
+      </c>
+      <c r="E453" s="3" t="s">
         <v>2315</v>
       </c>
-      <c r="D453" s="3" t="s">
+      <c r="F453" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G453" s="3" t="s">
         <v>2316</v>
-      </c>
-      <c r="E453" s="3" t="s">
-        <v>2317</v>
-      </c>
-      <c r="F453" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G453" s="3" t="s">
-        <v>2318</v>
       </c>
       <c r="H453" s="3" t="s">
         <v>15</v>
@@ -19867,103 +19960,103 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="3" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B454" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C454" s="3" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D454" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="E454" s="3" t="s">
         <v>2319</v>
       </c>
-      <c r="B454" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C454" s="3" t="s">
+      <c r="F454" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G454" s="3" t="s">
         <v>2320</v>
       </c>
-      <c r="D454" s="3" t="s">
+      <c r="H454" s="3" t="s">
         <v>2321</v>
-      </c>
-      <c r="E454" s="3" t="s">
-        <v>2322</v>
-      </c>
-      <c r="F454" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G454" s="3" t="s">
-        <v>2323</v>
-      </c>
-      <c r="H454" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="3" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B455" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C455" s="3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D455" s="3" t="s">
         <v>2324</v>
       </c>
-      <c r="B455" s="3" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C455" s="3" t="s">
+      <c r="E455" s="3" t="s">
         <v>2325</v>
       </c>
-      <c r="D455" s="3" t="s">
+      <c r="F455" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G455" s="3" t="s">
         <v>2326</v>
       </c>
-      <c r="E455" s="3" t="s">
+      <c r="H455" s="3" t="s">
         <v>2327</v>
-      </c>
-      <c r="F455" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G455" s="3" t="s">
-        <v>2328</v>
-      </c>
-      <c r="H455" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D456" s="3" t="s">
         <v>2329</v>
       </c>
-      <c r="B456" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C456" s="3" t="s">
+      <c r="E456" s="3" t="s">
         <v>2330</v>
       </c>
-      <c r="D456" s="3" t="s">
+      <c r="F456" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G456" s="3" t="s">
         <v>2331</v>
       </c>
-      <c r="E456" s="3" t="s">
+      <c r="H456" s="3" t="s">
         <v>2332</v>
-      </c>
-      <c r="F456" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G456" s="3" t="s">
-        <v>2333</v>
-      </c>
-      <c r="H456" s="3" t="s">
-        <v>2334</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="3" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D457" s="3" t="s">
         <v>2335</v>
       </c>
-      <c r="B457" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C457" s="3" t="s">
-        <v>2330</v>
-      </c>
-      <c r="D457" s="3" t="s">
+      <c r="E457" s="3" t="s">
         <v>2336</v>
       </c>
-      <c r="E457" s="3" t="s">
+      <c r="F457" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G457" s="3" t="s">
         <v>2337</v>
-      </c>
-      <c r="F457" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G457" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="H457" s="3" t="s">
         <v>2338</v>
@@ -19974,7 +20067,7 @@
         <v>2339</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>1160</v>
+        <v>1598</v>
       </c>
       <c r="C458" s="3" t="s">
         <v>2340</v>
@@ -20000,22 +20093,22 @@
         <v>2345</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>59</v>
+        <v>298</v>
       </c>
       <c r="C459" s="3" t="s">
-        <v>65</v>
+        <v>2346</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G459" s="3" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="H459" s="3" t="s">
         <v>15</v>
@@ -20023,210 +20116,210 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="3" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>500</v>
+        <v>298</v>
       </c>
       <c r="C460" s="3" t="s">
-        <v>1384</v>
+        <v>2351</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="F460" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G460" s="3" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="H460" s="3" t="s">
-        <v>2353</v>
+        <v>15</v>
       </c>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="3" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>500</v>
+        <v>1129</v>
       </c>
       <c r="C461" s="3" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G461" s="3" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="H461" s="3" t="s">
-        <v>2353</v>
+        <v>15</v>
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>500</v>
+        <v>362</v>
       </c>
       <c r="C462" s="3" t="s">
-        <v>2355</v>
+        <v>2361</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G462" s="3" t="s">
-        <v>2358</v>
+        <v>2364</v>
       </c>
       <c r="H462" s="3" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="3" t="s">
-        <v>2363</v>
+        <v>2366</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>500</v>
+        <v>362</v>
       </c>
       <c r="C463" s="3" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G463" s="3" t="s">
-        <v>2367</v>
+        <v>235</v>
       </c>
       <c r="H463" s="3" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>500</v>
+        <v>1160</v>
       </c>
       <c r="C464" s="3" t="s">
-        <v>2355</v>
+        <v>2371</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G464" s="3" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="H464" s="3" t="s">
-        <v>15</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="3" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>500</v>
+        <v>59</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>2374</v>
+        <v>65</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G465" s="3" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="H465" s="3" t="s">
-        <v>2353</v>
+        <v>15</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" s="3" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>500</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>2379</v>
+        <v>1384</v>
       </c>
       <c r="D466" s="3" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="E466" s="3" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G466" s="3" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="H466" s="3" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>500</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="E467" s="3" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G467" s="3" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="H467" s="3" t="s">
-        <v>2389</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.25">
@@ -20234,140 +20327,140 @@
         <v>2390</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>362</v>
+        <v>500</v>
       </c>
       <c r="C468" s="3" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D468" s="3" t="s">
         <v>2391</v>
-      </c>
-      <c r="D468" s="3" t="s">
-        <v>2356</v>
       </c>
       <c r="E468" s="3" t="s">
         <v>2392</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G468" s="3" t="s">
+        <v>2389</v>
+      </c>
+      <c r="H468" s="3" t="s">
         <v>2393</v>
-      </c>
-      <c r="H468" s="3" t="s">
-        <v>2394</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="3" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B469" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C469" s="3" t="s">
         <v>2395</v>
       </c>
-      <c r="B469" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C469" s="3" t="s">
+      <c r="D469" s="3" t="s">
         <v>2396</v>
       </c>
-      <c r="D469" s="3" t="s">
+      <c r="E469" s="3" t="s">
         <v>2397</v>
       </c>
-      <c r="E469" s="3" t="s">
+      <c r="F469" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G469" s="3" t="s">
         <v>2398</v>
       </c>
-      <c r="F469" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G469" s="3" t="s">
+      <c r="H469" s="3" t="s">
         <v>2399</v>
-      </c>
-      <c r="H469" s="3" t="s">
-        <v>2400</v>
       </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B470" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D470" s="3" t="s">
         <v>2401</v>
       </c>
-      <c r="B470" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C470" s="3" t="s">
+      <c r="E470" s="3" t="s">
         <v>2402</v>
       </c>
-      <c r="D470" s="3" t="s">
+      <c r="F470" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G470" s="3" t="s">
         <v>2403</v>
       </c>
-      <c r="E470" s="3" t="s">
-        <v>2404</v>
-      </c>
-      <c r="F470" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G470" s="3" t="s">
-        <v>2393</v>
-      </c>
       <c r="H470" s="3" t="s">
-        <v>2405</v>
+        <v>15</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>500</v>
       </c>
       <c r="C471" s="3" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D471" s="3" t="s">
+        <v>2406</v>
+      </c>
+      <c r="E471" s="3" t="s">
         <v>2407</v>
       </c>
-      <c r="D471" s="3" t="s">
+      <c r="F471" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G471" s="3" t="s">
         <v>2408</v>
       </c>
-      <c r="E471" s="3" t="s">
-        <v>2409</v>
-      </c>
-      <c r="F471" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G471" s="3" t="s">
-        <v>2410</v>
-      </c>
       <c r="H471" s="3" t="s">
-        <v>2411</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="3" t="s">
-        <v>2412</v>
+        <v>2409</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>500</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>2413</v>
+        <v>2410</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>2414</v>
+        <v>2411</v>
       </c>
       <c r="E472" s="3" t="s">
-        <v>2415</v>
+        <v>2412</v>
       </c>
       <c r="F472" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G472" s="3" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="H472" s="3" t="s">
-        <v>2353</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>500</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>1395</v>
+        <v>2416</v>
       </c>
       <c r="D473" s="3" t="s">
         <v>2417</v>
@@ -20376,180 +20469,180 @@
         <v>2418</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G473" s="3" t="s">
-        <v>2410</v>
+        <v>2419</v>
       </c>
       <c r="H473" s="3" t="s">
-        <v>2353</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>500</v>
+        <v>362</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>1395</v>
+        <v>2422</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>2420</v>
+        <v>2387</v>
       </c>
       <c r="E474" s="3" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G474" s="3" t="s">
-        <v>2410</v>
+        <v>2424</v>
       </c>
       <c r="H474" s="3" t="s">
-        <v>2353</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" s="3" t="s">
-        <v>2422</v>
+        <v>2426</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>500</v>
+        <v>362</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>1395</v>
+        <v>2427</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>2423</v>
+        <v>2428</v>
       </c>
       <c r="E475" s="3" t="s">
-        <v>2424</v>
+        <v>2429</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G475" s="3" t="s">
-        <v>2425</v>
+        <v>2430</v>
       </c>
       <c r="H475" s="3" t="s">
-        <v>2426</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
-        <v>2427</v>
+        <v>2432</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>805</v>
+        <v>362</v>
       </c>
       <c r="C476" s="3" t="s">
-        <v>933</v>
+        <v>2433</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>2428</v>
+        <v>2434</v>
       </c>
       <c r="E476" s="3" t="s">
-        <v>2429</v>
+        <v>2435</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G476" s="3" t="s">
-        <v>2430</v>
+        <v>2424</v>
       </c>
       <c r="H476" s="3" t="s">
-        <v>2431</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
-        <v>2432</v>
+        <v>2437</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>805</v>
+        <v>500</v>
       </c>
       <c r="C477" s="3" t="s">
-        <v>933</v>
+        <v>2438</v>
       </c>
       <c r="D477" s="3" t="s">
-        <v>2433</v>
+        <v>2439</v>
       </c>
       <c r="E477" s="3" t="s">
-        <v>2434</v>
+        <v>2440</v>
       </c>
       <c r="F477" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G477" s="3" t="s">
-        <v>2435</v>
+        <v>2441</v>
       </c>
       <c r="H477" s="3" t="s">
-        <v>2436</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="3" t="s">
-        <v>2437</v>
+        <v>2443</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>805</v>
+        <v>500</v>
       </c>
       <c r="C478" s="3" t="s">
-        <v>2438</v>
+        <v>2444</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>2439</v>
+        <v>2445</v>
       </c>
       <c r="E478" s="3" t="s">
-        <v>2440</v>
+        <v>2446</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G478" s="3" t="s">
         <v>2441</v>
       </c>
       <c r="H478" s="3" t="s">
-        <v>2442</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
-        <v>2443</v>
+        <v>2447</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>805</v>
+        <v>500</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>2444</v>
+        <v>1395</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
       <c r="E479" s="3" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
       <c r="F479" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G479" s="3" t="s">
-        <v>2447</v>
+        <v>2441</v>
       </c>
       <c r="H479" s="3" t="s">
-        <v>2448</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="3" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>805</v>
+        <v>500</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>2450</v>
+        <v>1395</v>
       </c>
       <c r="D480" s="3" t="s">
         <v>2451</v>
@@ -20558,313 +20651,313 @@
         <v>2452</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G480" s="3" t="s">
-        <v>2453</v>
+        <v>2441</v>
       </c>
       <c r="H480" s="3" t="s">
-        <v>2454</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="3" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B481" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C481" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D481" s="3" t="s">
+        <v>2454</v>
+      </c>
+      <c r="E481" s="3" t="s">
         <v>2455</v>
       </c>
-      <c r="B481" s="3" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C481" s="3" t="s">
+      <c r="F481" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G481" s="3" t="s">
         <v>2456</v>
       </c>
-      <c r="D481" s="3" t="s">
+      <c r="H481" s="3" t="s">
         <v>2457</v>
-      </c>
-      <c r="E481" s="3" t="s">
-        <v>2458</v>
-      </c>
-      <c r="F481" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G481" s="3" t="s">
-        <v>2459</v>
-      </c>
-      <c r="H481" s="3" t="s">
-        <v>2460</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B482" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C482" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="D482" s="3" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E482" s="3" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F482" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G482" s="3" t="s">
         <v>2461</v>
       </c>
-      <c r="B482" s="3" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C482" s="3" t="s">
+      <c r="H482" s="3" t="s">
         <v>2462</v>
-      </c>
-      <c r="D482" s="3" t="s">
-        <v>2463</v>
-      </c>
-      <c r="E482" s="3" t="s">
-        <v>2464</v>
-      </c>
-      <c r="F482" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G482" s="3" t="s">
-        <v>2465</v>
-      </c>
-      <c r="H482" s="3" t="s">
-        <v>2466</v>
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="3" t="s">
-        <v>2467</v>
+        <v>2463</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>805</v>
       </c>
       <c r="C483" s="3" t="s">
-        <v>2468</v>
+        <v>933</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>2469</v>
+        <v>2464</v>
       </c>
       <c r="E483" s="3" t="s">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="F483" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G483" s="3" t="s">
-        <v>2471</v>
+        <v>2466</v>
       </c>
       <c r="H483" s="3" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="3" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B484" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C484" s="3" t="s">
+        <v>2469</v>
+      </c>
+      <c r="D484" s="3" t="s">
+        <v>2470</v>
+      </c>
+      <c r="E484" s="3" t="s">
+        <v>2471</v>
+      </c>
+      <c r="F484" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G484" s="3" t="s">
+        <v>2472</v>
+      </c>
+      <c r="H484" s="3" t="s">
         <v>2473</v>
-      </c>
-      <c r="B484" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C484" s="3" t="s">
-        <v>2474</v>
-      </c>
-      <c r="D484" s="3" t="s">
-        <v>2475</v>
-      </c>
-      <c r="E484" s="3" t="s">
-        <v>2476</v>
-      </c>
-      <c r="F484" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G484" s="3" t="s">
-        <v>2477</v>
-      </c>
-      <c r="H484" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="3" t="s">
-        <v>2478</v>
+        <v>2474</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>805</v>
       </c>
       <c r="C485" s="3" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D485" s="3" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E485" s="3" t="s">
+        <v>2477</v>
+      </c>
+      <c r="F485" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G485" s="3" t="s">
+        <v>2478</v>
+      </c>
+      <c r="H485" s="3" t="s">
         <v>2479</v>
-      </c>
-      <c r="D485" s="3" t="s">
-        <v>2480</v>
-      </c>
-      <c r="E485" s="3" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F485" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G485" s="3" t="s">
-        <v>2482</v>
-      </c>
-      <c r="H485" s="3" t="s">
-        <v>2483</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
+        <v>2480</v>
+      </c>
+      <c r="B486" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C486" s="3" t="s">
+        <v>2481</v>
+      </c>
+      <c r="D486" s="3" t="s">
+        <v>2482</v>
+      </c>
+      <c r="E486" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="F486" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G486" s="3" t="s">
         <v>2484</v>
       </c>
-      <c r="B486" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C486" s="3" t="s">
+      <c r="H486" s="3" t="s">
         <v>2485</v>
-      </c>
-      <c r="D486" s="3" t="s">
-        <v>2486</v>
-      </c>
-      <c r="E486" s="3" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F486" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G486" s="3" t="s">
-        <v>2488</v>
-      </c>
-      <c r="H486" s="3" t="s">
-        <v>2489</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="3" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C487" s="3" t="s">
+        <v>2487</v>
+      </c>
+      <c r="D487" s="3" t="s">
+        <v>2488</v>
+      </c>
+      <c r="E487" s="3" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F487" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G487" s="3" t="s">
         <v>2490</v>
       </c>
-      <c r="B487" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C487" s="3" t="s">
+      <c r="H487" s="3" t="s">
         <v>2491</v>
-      </c>
-      <c r="D487" s="3" t="s">
-        <v>2492</v>
-      </c>
-      <c r="E487" s="3" t="s">
-        <v>2493</v>
-      </c>
-      <c r="F487" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G487" s="3" t="s">
-        <v>2494</v>
-      </c>
-      <c r="H487" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D488" s="3" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E488" s="3" t="s">
         <v>2495</v>
       </c>
-      <c r="B488" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C488" s="3" t="s">
+      <c r="F488" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G488" s="3" t="s">
         <v>2496</v>
       </c>
-      <c r="D488" s="3" t="s">
-        <v>1385</v>
-      </c>
-      <c r="E488" s="3" t="s">
+      <c r="H488" s="3" t="s">
         <v>2497</v>
-      </c>
-      <c r="F488" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G488" s="3" t="s">
-        <v>2498</v>
-      </c>
-      <c r="H488" s="3" t="s">
-        <v>2499</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="3" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C489" s="3" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D489" s="3" t="s">
         <v>2500</v>
       </c>
-      <c r="B489" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C489" s="3" t="s">
+      <c r="E489" s="3" t="s">
         <v>2501</v>
       </c>
-      <c r="D489" s="3" t="s">
+      <c r="F489" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G489" s="3" t="s">
         <v>2502</v>
       </c>
-      <c r="E489" s="3" t="s">
+      <c r="H489" s="3" t="s">
         <v>2503</v>
-      </c>
-      <c r="F489" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G489" s="3" t="s">
-        <v>2504</v>
-      </c>
-      <c r="H489" s="3" t="s">
-        <v>2505</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>362</v>
       </c>
       <c r="C490" s="3" t="s">
-        <v>2485</v>
+        <v>2505</v>
       </c>
       <c r="D490" s="3" t="s">
+        <v>2506</v>
+      </c>
+      <c r="E490" s="3" t="s">
         <v>2507</v>
       </c>
-      <c r="E490" s="3" t="s">
+      <c r="F490" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G490" s="3" t="s">
         <v>2508</v>
       </c>
-      <c r="F490" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G490" s="3" t="s">
-        <v>2509</v>
-      </c>
       <c r="H490" s="3" t="s">
-        <v>2510</v>
+        <v>15</v>
       </c>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C491" s="3" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D491" s="3" t="s">
         <v>2511</v>
       </c>
-      <c r="B491" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C491" s="3" t="s">
+      <c r="E491" s="3" t="s">
         <v>2512</v>
       </c>
-      <c r="D491" s="3" t="s">
+      <c r="F491" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G491" s="3" t="s">
         <v>2513</v>
       </c>
-      <c r="E491" s="3" t="s">
+      <c r="H491" s="3" t="s">
         <v>2514</v>
-      </c>
-      <c r="F491" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G491" s="3" t="s">
-        <v>2504</v>
-      </c>
-      <c r="H491" s="3" t="s">
-        <v>2515</v>
       </c>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>362</v>
       </c>
       <c r="C492" s="3" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D492" s="3" t="s">
         <v>2517</v>
-      </c>
-      <c r="D492" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="E492" s="3" t="s">
         <v>2518</v>
@@ -20873,114 +20966,270 @@
         <v>27</v>
       </c>
       <c r="G492" s="3" t="s">
-        <v>2509</v>
+        <v>2519</v>
       </c>
       <c r="H492" s="3" t="s">
-        <v>2483</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" s="3" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>362</v>
       </c>
       <c r="C493" s="3" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="D493" s="3" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="E493" s="3" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="F493" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G493" s="3" t="s">
-        <v>2509</v>
+        <v>2525</v>
       </c>
       <c r="H493" s="3" t="s">
-        <v>2483</v>
+        <v>15</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>362</v>
       </c>
       <c r="C494" s="3" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>1385</v>
       </c>
       <c r="E494" s="3" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
       <c r="F494" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G494" s="3" t="s">
-        <v>2509</v>
+        <v>2529</v>
       </c>
       <c r="H494" s="3" t="s">
-        <v>2483</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
-        <v>2526</v>
+        <v>2531</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>500</v>
+        <v>362</v>
       </c>
       <c r="C495" s="3" t="s">
-        <v>2527</v>
+        <v>2532</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>2528</v>
+        <v>2533</v>
       </c>
       <c r="E495" s="3" t="s">
-        <v>2529</v>
+        <v>2534</v>
       </c>
       <c r="F495" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G495" s="3" t="s">
-        <v>2530</v>
+        <v>2535</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>2531</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
-        <v>2532</v>
+        <v>2537</v>
       </c>
       <c r="B496" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C496" s="3" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D496" s="3" t="s">
+        <v>2538</v>
+      </c>
+      <c r="E496" s="3" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F496" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G496" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="H496" s="3" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A497" s="3" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C497" s="3" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D497" s="3" t="s">
+        <v>2544</v>
+      </c>
+      <c r="E497" s="3" t="s">
+        <v>2545</v>
+      </c>
+      <c r="F497" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G497" s="3" t="s">
+        <v>2535</v>
+      </c>
+      <c r="H497" s="3" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A498" s="3" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C498" s="3" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D498" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E498" s="3" t="s">
+        <v>2549</v>
+      </c>
+      <c r="F498" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G498" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="H498" s="3" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A499" s="3" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B499" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C499" s="3" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D499" s="3" t="s">
+        <v>2552</v>
+      </c>
+      <c r="E499" s="3" t="s">
+        <v>2553</v>
+      </c>
+      <c r="F499" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G499" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="H499" s="3" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A500" s="3" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B500" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C500" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D500" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E500" s="3" t="s">
+        <v>2556</v>
+      </c>
+      <c r="F500" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G500" s="3" t="s">
+        <v>2540</v>
+      </c>
+      <c r="H500" s="3" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A501" s="3" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C501" s="3" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D501" s="3" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E501" s="3" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F501" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G501" s="3" t="s">
+        <v>2561</v>
+      </c>
+      <c r="H501" s="3" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A502" s="3" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B502" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="C496" s="3" t="s">
-        <v>2533</v>
-      </c>
-      <c r="D496" s="3" t="s">
-        <v>2534</v>
-      </c>
-      <c r="E496" s="3" t="s">
-        <v>2535</v>
-      </c>
-      <c r="F496" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G496" s="3" t="s">
-        <v>2536</v>
-      </c>
-      <c r="H496" s="3" t="s">
-        <v>2537</v>
+      <c r="C502" s="3" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D502" s="3" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E502" s="3" t="s">
+        <v>2566</v>
+      </c>
+      <c r="F502" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G502" s="3" t="s">
+        <v>2567</v>
+      </c>
+      <c r="H502" s="3" t="s">
+        <v>2568</v>
       </c>
     </row>
   </sheetData>
@@ -21001,82 +21250,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>2538</v>
+        <v>2569</v>
       </c>
       <c r="B1" t="s">
-        <v>2539</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>2540</v>
+        <v>2571</v>
       </c>
       <c r="B2" t="s">
-        <v>2541</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>2542</v>
+        <v>2573</v>
       </c>
       <c r="B3" t="s">
-        <v>2543</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>2544</v>
+        <v>2575</v>
       </c>
       <c r="B4" t="s">
-        <v>2545</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>2546</v>
+        <v>2577</v>
       </c>
       <c r="B5" t="s">
-        <v>2547</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>2548</v>
+        <v>2579</v>
       </c>
       <c r="B6" t="s">
-        <v>2549</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>2550</v>
+        <v>2581</v>
       </c>
       <c r="B7" t="s">
-        <v>2551</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>2552</v>
+        <v>2583</v>
       </c>
       <c r="B8" t="s">
-        <v>2553</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>2552</v>
+        <v>2583</v>
       </c>
       <c r="B9" t="s">
-        <v>2554</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>2552</v>
+        <v>2583</v>
       </c>
       <c r="B10" t="s">
-        <v>2555</v>
+        <v>2586</v>
       </c>
     </row>
   </sheetData>
